--- a/Excel/ResData.xlsx
+++ b/Excel/ResData.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="30720" windowHeight="13380"/>
+    <workbookView windowWidth="22091" windowHeight="9527"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="101">
   <si>
     <t>int</t>
   </si>
@@ -116,6 +116,9 @@
     <t>SO</t>
   </si>
   <si>
+    <t>VFX</t>
+  </si>
+  <si>
     <t>预制体</t>
   </si>
   <si>
@@ -143,6 +146,9 @@
     <t>ScriptableObject</t>
   </si>
   <si>
+    <t>特效</t>
+  </si>
+  <si>
     <t>GameStartPanel</t>
   </si>
   <si>
@@ -161,79 +167,139 @@
     <t>prefab</t>
   </si>
   <si>
-    <t>Blue</t>
-  </si>
-  <si>
-    <t>蓝色材质</t>
-  </si>
-  <si>
-    <t>Materials/Blue</t>
-  </si>
-  <si>
-    <t>ArtRes/Materials/Blue</t>
+    <t>GameEndPanel</t>
+  </si>
+  <si>
+    <t>结束面板</t>
+  </si>
+  <si>
+    <t>UI/Panel/GameEndPanel</t>
+  </si>
+  <si>
+    <t>ArtRes/UI/Panel/GameEndPanel</t>
+  </si>
+  <si>
+    <t>卡牌1</t>
+  </si>
+  <si>
+    <t>Materials/1</t>
+  </si>
+  <si>
+    <t>ArtRes/Materials/1</t>
+  </si>
+  <si>
+    <t>materials</t>
   </si>
   <si>
     <t>mat</t>
   </si>
   <si>
-    <t>Green</t>
-  </si>
-  <si>
-    <t>绿色材质</t>
-  </si>
-  <si>
-    <t>Materials/Green</t>
-  </si>
-  <si>
-    <t>ArtRes/Materials/Green</t>
-  </si>
-  <si>
-    <t>Orange</t>
-  </si>
-  <si>
-    <t>橙色材质</t>
-  </si>
-  <si>
-    <t>Materials/Orange</t>
-  </si>
-  <si>
-    <t>ArtRes/Materials/Orange</t>
-  </si>
-  <si>
-    <t>Pink</t>
-  </si>
-  <si>
-    <t>粉色材质</t>
-  </si>
-  <si>
-    <t>Materials/Pink</t>
-  </si>
-  <si>
-    <t>ArtRes/Materials/Pink</t>
-  </si>
-  <si>
-    <t>Red</t>
-  </si>
-  <si>
-    <t>红色材质</t>
-  </si>
-  <si>
-    <t>Materials/Red</t>
-  </si>
-  <si>
-    <t>ArtRes/Materials/Red</t>
-  </si>
-  <si>
-    <t>Yellow</t>
-  </si>
-  <si>
-    <t>黄色材质</t>
-  </si>
-  <si>
-    <t>Materials/Yellow</t>
-  </si>
-  <si>
-    <t>ArtRes/Materials/Yellow</t>
+    <t>卡牌2</t>
+  </si>
+  <si>
+    <t>Materials/2</t>
+  </si>
+  <si>
+    <t>ArtRes/Materials/2</t>
+  </si>
+  <si>
+    <t>卡牌3</t>
+  </si>
+  <si>
+    <t>Materials/3</t>
+  </si>
+  <si>
+    <t>ArtRes/Materials/3</t>
+  </si>
+  <si>
+    <t>卡牌4</t>
+  </si>
+  <si>
+    <t>Materials/4</t>
+  </si>
+  <si>
+    <t>ArtRes/Materials/4</t>
+  </si>
+  <si>
+    <t>卡牌5</t>
+  </si>
+  <si>
+    <t>Materials/5</t>
+  </si>
+  <si>
+    <t>ArtRes/Materials/5</t>
+  </si>
+  <si>
+    <t>卡牌6</t>
+  </si>
+  <si>
+    <t>Materials/6</t>
+  </si>
+  <si>
+    <t>ArtRes/Materials/6</t>
+  </si>
+  <si>
+    <t>卡牌7</t>
+  </si>
+  <si>
+    <t>Materials/7</t>
+  </si>
+  <si>
+    <t>ArtRes/Materials/7</t>
+  </si>
+  <si>
+    <t>卡牌8</t>
+  </si>
+  <si>
+    <t>Materials/8</t>
+  </si>
+  <si>
+    <t>ArtRes/Materials/8</t>
+  </si>
+  <si>
+    <t>卡牌9</t>
+  </si>
+  <si>
+    <t>Materials/9</t>
+  </si>
+  <si>
+    <t>ArtRes/Materials/9</t>
+  </si>
+  <si>
+    <t>卡牌10</t>
+  </si>
+  <si>
+    <t>Materials/10</t>
+  </si>
+  <si>
+    <t>ArtRes/Materials/10</t>
+  </si>
+  <si>
+    <t>卡牌11</t>
+  </si>
+  <si>
+    <t>Materials/11</t>
+  </si>
+  <si>
+    <t>ArtRes/Materials/11</t>
+  </si>
+  <si>
+    <t>卡牌12</t>
+  </si>
+  <si>
+    <t>Materials/12</t>
+  </si>
+  <si>
+    <t>ArtRes/Materials/12</t>
+  </si>
+  <si>
+    <t>BG</t>
+  </si>
+  <si>
+    <t>Materials/BG</t>
+  </si>
+  <si>
+    <t>ArtRes/Materials/BG</t>
   </si>
   <si>
     <t>Card</t>
@@ -246,6 +312,24 @@
   </si>
   <si>
     <t>ArtRes/Prefabs/Card</t>
+  </si>
+  <si>
+    <t>prefabs</t>
+  </si>
+  <si>
+    <t>Success</t>
+  </si>
+  <si>
+    <t>成功特效</t>
+  </si>
+  <si>
+    <t>VFX/Success</t>
+  </si>
+  <si>
+    <t>ArtRes/VFX/Success</t>
+  </si>
+  <si>
+    <t>vfx</t>
   </si>
 </sst>
 </file>
@@ -1393,7 +1477,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J20"/>
+  <dimension ref="A1:K29"/>
   <sheetFormatPr defaultColWidth="9.23148148148148" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="12.1759259259259" customWidth="1"/>
@@ -1407,7 +1491,7 @@
     <col min="10" max="10" width="15.8518518518519" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:11">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1433,7 +1517,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" ht="101" customHeight="1" spans="1:10">
+    <row r="2" ht="101" customHeight="1" spans="1:11">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -1459,7 +1543,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:11">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -1485,7 +1569,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:11">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -1516,8 +1600,11 @@
       <c r="J4">
         <v>9</v>
       </c>
-    </row>
-    <row r="5" spans="1:10">
+      <c r="K4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -1548,97 +1635,103 @@
       <c r="J5" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="6" spans="1:10">
+      <c r="K5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
       <c r="A6" t="s">
         <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J6" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10">
+        <v>38</v>
+      </c>
+      <c r="K6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
       <c r="A13">
         <v>1</v>
       </c>
       <c r="B13" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C13" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D13">
         <v>0</v>
       </c>
       <c r="E13" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F13" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G13" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H13" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
       <c r="A14">
+        <v>2</v>
+      </c>
+      <c r="B14" t="s">
+        <v>46</v>
+      </c>
+      <c r="C14" t="s">
+        <v>47</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
+      </c>
+      <c r="E14" t="s">
+        <v>48</v>
+      </c>
+      <c r="F14" t="s">
+        <v>49</v>
+      </c>
+      <c r="G14" t="s">
+        <v>44</v>
+      </c>
+      <c r="H14" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="A15">
         <v>10001</v>
       </c>
-      <c r="B14" t="s">
-        <v>44</v>
-      </c>
-      <c r="C14" t="s">
-        <v>45</v>
-      </c>
-      <c r="D14">
-        <v>4</v>
-      </c>
-      <c r="E14" t="s">
-        <v>46</v>
-      </c>
-      <c r="F14" t="s">
-        <v>47</v>
-      </c>
-      <c r="G14" t="s">
-        <v>24</v>
-      </c>
-      <c r="H14" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="15" customFormat="1" spans="1:10">
-      <c r="A15">
-        <v>10002</v>
-      </c>
-      <c r="B15" t="s">
-        <v>49</v>
+      <c r="B15">
+        <v>1</v>
       </c>
       <c r="C15" t="s">
         <v>50</v>
@@ -1653,44 +1746,44 @@
         <v>52</v>
       </c>
       <c r="G15" t="s">
-        <v>24</v>
+        <v>53</v>
       </c>
       <c r="H15" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="16" customFormat="1" spans="1:10">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="16" customFormat="1" spans="1:11">
       <c r="A16">
-        <v>10003</v>
-      </c>
-      <c r="B16" t="s">
-        <v>53</v>
+        <v>10002</v>
+      </c>
+      <c r="B16">
+        <v>2</v>
       </c>
       <c r="C16" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D16">
         <v>4</v>
       </c>
       <c r="E16" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F16" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G16" t="s">
-        <v>24</v>
+        <v>53</v>
       </c>
       <c r="H16" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
     </row>
     <row r="17" customFormat="1" spans="1:8">
       <c r="A17">
-        <v>10004</v>
-      </c>
-      <c r="B17" t="s">
-        <v>57</v>
+        <v>10003</v>
+      </c>
+      <c r="B17">
+        <v>3</v>
       </c>
       <c r="C17" t="s">
         <v>58</v>
@@ -1705,88 +1798,322 @@
         <v>60</v>
       </c>
       <c r="G17" t="s">
-        <v>24</v>
+        <v>53</v>
       </c>
       <c r="H17" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
     </row>
     <row r="18" customFormat="1" spans="1:8">
       <c r="A18">
-        <v>10005</v>
-      </c>
-      <c r="B18" t="s">
+        <v>10004</v>
+      </c>
+      <c r="B18">
+        <v>4</v>
+      </c>
+      <c r="C18" t="s">
         <v>61</v>
-      </c>
-      <c r="C18" t="s">
-        <v>62</v>
       </c>
       <c r="D18">
         <v>4</v>
       </c>
       <c r="E18" t="s">
+        <v>62</v>
+      </c>
+      <c r="F18" t="s">
         <v>63</v>
       </c>
-      <c r="F18" t="s">
-        <v>64</v>
-      </c>
       <c r="G18" t="s">
-        <v>24</v>
+        <v>53</v>
       </c>
       <c r="H18" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19" customFormat="1" spans="1:8">
       <c r="A19">
-        <v>10006</v>
-      </c>
-      <c r="B19" t="s">
-        <v>65</v>
+        <v>10005</v>
+      </c>
+      <c r="B19">
+        <v>5</v>
       </c>
       <c r="C19" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D19">
         <v>4</v>
       </c>
       <c r="E19" t="s">
+        <v>65</v>
+      </c>
+      <c r="F19" t="s">
+        <v>66</v>
+      </c>
+      <c r="G19" t="s">
+        <v>53</v>
+      </c>
+      <c r="H19" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="20" customFormat="1" spans="1:8">
+      <c r="A20">
+        <v>10006</v>
+      </c>
+      <c r="B20">
+        <v>6</v>
+      </c>
+      <c r="C20" t="s">
         <v>67</v>
       </c>
-      <c r="F19" t="s">
+      <c r="D20">
+        <v>4</v>
+      </c>
+      <c r="E20" t="s">
         <v>68</v>
       </c>
-      <c r="G19" t="s">
-        <v>24</v>
-      </c>
-      <c r="H19" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8">
-      <c r="A20">
+      <c r="F20" t="s">
+        <v>69</v>
+      </c>
+      <c r="G20" t="s">
+        <v>53</v>
+      </c>
+      <c r="H20" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="21" customFormat="1" spans="1:8">
+      <c r="A21">
+        <v>10007</v>
+      </c>
+      <c r="B21">
+        <v>7</v>
+      </c>
+      <c r="C21" t="s">
+        <v>70</v>
+      </c>
+      <c r="D21">
+        <v>4</v>
+      </c>
+      <c r="E21" t="s">
+        <v>71</v>
+      </c>
+      <c r="F21" t="s">
+        <v>72</v>
+      </c>
+      <c r="G21" t="s">
+        <v>53</v>
+      </c>
+      <c r="H21" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="22" customFormat="1" spans="1:8">
+      <c r="A22">
+        <v>10008</v>
+      </c>
+      <c r="B22">
+        <v>8</v>
+      </c>
+      <c r="C22" t="s">
+        <v>73</v>
+      </c>
+      <c r="D22">
+        <v>4</v>
+      </c>
+      <c r="E22" t="s">
+        <v>74</v>
+      </c>
+      <c r="F22" t="s">
+        <v>75</v>
+      </c>
+      <c r="G22" t="s">
+        <v>53</v>
+      </c>
+      <c r="H22" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="23" customFormat="1" spans="1:8">
+      <c r="A23">
+        <v>10009</v>
+      </c>
+      <c r="B23">
+        <v>9</v>
+      </c>
+      <c r="C23" t="s">
+        <v>76</v>
+      </c>
+      <c r="D23">
+        <v>4</v>
+      </c>
+      <c r="E23" t="s">
+        <v>77</v>
+      </c>
+      <c r="F23" t="s">
+        <v>78</v>
+      </c>
+      <c r="G23" t="s">
+        <v>53</v>
+      </c>
+      <c r="H23" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="24" customFormat="1" spans="1:8">
+      <c r="A24">
+        <v>10010</v>
+      </c>
+      <c r="B24">
+        <v>10</v>
+      </c>
+      <c r="C24" t="s">
+        <v>79</v>
+      </c>
+      <c r="D24">
+        <v>4</v>
+      </c>
+      <c r="E24" t="s">
+        <v>80</v>
+      </c>
+      <c r="F24" t="s">
+        <v>81</v>
+      </c>
+      <c r="G24" t="s">
+        <v>53</v>
+      </c>
+      <c r="H24" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="25" customFormat="1" spans="1:8">
+      <c r="A25">
+        <v>10011</v>
+      </c>
+      <c r="B25">
+        <v>11</v>
+      </c>
+      <c r="C25" t="s">
+        <v>82</v>
+      </c>
+      <c r="D25">
+        <v>4</v>
+      </c>
+      <c r="E25" t="s">
+        <v>83</v>
+      </c>
+      <c r="F25" t="s">
+        <v>84</v>
+      </c>
+      <c r="G25" t="s">
+        <v>53</v>
+      </c>
+      <c r="H25" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="26" customFormat="1" spans="1:8">
+      <c r="A26">
+        <v>10012</v>
+      </c>
+      <c r="B26">
+        <v>12</v>
+      </c>
+      <c r="C26" t="s">
+        <v>85</v>
+      </c>
+      <c r="D26">
+        <v>4</v>
+      </c>
+      <c r="E26" t="s">
+        <v>86</v>
+      </c>
+      <c r="F26" t="s">
+        <v>87</v>
+      </c>
+      <c r="G26" t="s">
+        <v>53</v>
+      </c>
+      <c r="H26" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="27" customFormat="1" spans="1:8">
+      <c r="A27">
+        <v>10013</v>
+      </c>
+      <c r="B27" t="s">
+        <v>88</v>
+      </c>
+      <c r="C27" t="s">
+        <v>85</v>
+      </c>
+      <c r="D27">
+        <v>4</v>
+      </c>
+      <c r="E27" t="s">
+        <v>89</v>
+      </c>
+      <c r="F27" t="s">
+        <v>90</v>
+      </c>
+      <c r="G27" t="s">
+        <v>53</v>
+      </c>
+      <c r="H27" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8">
+      <c r="A28">
         <v>20001</v>
       </c>
-      <c r="B20" t="s">
-        <v>69</v>
-      </c>
-      <c r="C20" t="s">
-        <v>70</v>
-      </c>
-      <c r="D20">
+      <c r="B28" t="s">
+        <v>91</v>
+      </c>
+      <c r="C28" t="s">
+        <v>92</v>
+      </c>
+      <c r="D28">
         <v>0</v>
       </c>
-      <c r="E20" t="s">
-        <v>71</v>
-      </c>
-      <c r="F20" t="s">
-        <v>72</v>
-      </c>
-      <c r="G20" t="s">
-        <v>20</v>
-      </c>
-      <c r="H20" t="s">
-        <v>43</v>
+      <c r="E28" t="s">
+        <v>93</v>
+      </c>
+      <c r="F28" t="s">
+        <v>94</v>
+      </c>
+      <c r="G28" t="s">
+        <v>95</v>
+      </c>
+      <c r="H28" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8">
+      <c r="A29">
+        <v>30001</v>
+      </c>
+      <c r="B29" t="s">
+        <v>96</v>
+      </c>
+      <c r="C29" t="s">
+        <v>97</v>
+      </c>
+      <c r="D29">
+        <v>10</v>
+      </c>
+      <c r="E29" t="s">
+        <v>98</v>
+      </c>
+      <c r="F29" t="s">
+        <v>99</v>
+      </c>
+      <c r="G29" t="s">
+        <v>100</v>
+      </c>
+      <c r="H29" t="s">
+        <v>45</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/ResData.xlsx
+++ b/Excel/ResData.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="109">
   <si>
     <t>int</t>
   </si>
@@ -177,6 +177,30 @@
   </si>
   <si>
     <t>ArtRes/UI/Panel/GameEndPanel</t>
+  </si>
+  <si>
+    <t>GameUIPanel</t>
+  </si>
+  <si>
+    <t>游戏面板</t>
+  </si>
+  <si>
+    <t>UI/Panel/GameUIPanel</t>
+  </si>
+  <si>
+    <t>ArtRes/UI/Panel/GameUIPanel</t>
+  </si>
+  <si>
+    <t>LevelPassPanel</t>
+  </si>
+  <si>
+    <t>通关面板</t>
+  </si>
+  <si>
+    <t>UI/Panel/LevelPassPanel</t>
+  </si>
+  <si>
+    <t>ArtRes/UI/Panel/LevelPassPanel</t>
   </si>
   <si>
     <t>卡牌1</t>
@@ -1477,7 +1501,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K29"/>
+  <dimension ref="A1:K31"/>
   <sheetFormatPr defaultColWidth="9.23148148148148" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="12.1759259259259" customWidth="1"/>
@@ -1726,44 +1750,44 @@
         <v>45</v>
       </c>
     </row>
-    <row r="15" spans="1:11">
+    <row r="15" customFormat="1" spans="1:11">
       <c r="A15">
-        <v>10001</v>
-      </c>
-      <c r="B15">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="B15" t="s">
+        <v>50</v>
       </c>
       <c r="C15" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D15">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E15" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F15" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G15" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="H15" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
     </row>
     <row r="16" customFormat="1" spans="1:11">
       <c r="A16">
-        <v>10002</v>
-      </c>
-      <c r="B16">
-        <v>2</v>
+        <v>4</v>
+      </c>
+      <c r="B16" t="s">
+        <v>54</v>
       </c>
       <c r="C16" t="s">
         <v>55</v>
       </c>
       <c r="D16">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E16" t="s">
         <v>56</v>
@@ -1772,18 +1796,18 @@
         <v>57</v>
       </c>
       <c r="G16" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="H16" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="17" customFormat="1" spans="1:8">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
       <c r="A17">
-        <v>10003</v>
+        <v>10001</v>
       </c>
       <c r="B17">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C17" t="s">
         <v>58</v>
@@ -1798,321 +1822,373 @@
         <v>60</v>
       </c>
       <c r="G17" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="H17" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
     </row>
     <row r="18" customFormat="1" spans="1:8">
       <c r="A18">
-        <v>10004</v>
+        <v>10002</v>
       </c>
       <c r="B18">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C18" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D18">
         <v>4</v>
       </c>
       <c r="E18" t="s">
+        <v>64</v>
+      </c>
+      <c r="F18" t="s">
+        <v>65</v>
+      </c>
+      <c r="G18" t="s">
+        <v>61</v>
+      </c>
+      <c r="H18" t="s">
         <v>62</v>
-      </c>
-      <c r="F18" t="s">
-        <v>63</v>
-      </c>
-      <c r="G18" t="s">
-        <v>53</v>
-      </c>
-      <c r="H18" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="19" customFormat="1" spans="1:8">
       <c r="A19">
-        <v>10005</v>
+        <v>10003</v>
       </c>
       <c r="B19">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C19" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D19">
         <v>4</v>
       </c>
       <c r="E19" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F19" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G19" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="H19" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
     </row>
     <row r="20" customFormat="1" spans="1:8">
       <c r="A20">
-        <v>10006</v>
+        <v>10004</v>
       </c>
       <c r="B20">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C20" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D20">
         <v>4</v>
       </c>
       <c r="E20" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F20" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G20" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="H20" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
     </row>
     <row r="21" customFormat="1" spans="1:8">
       <c r="A21">
-        <v>10007</v>
+        <v>10005</v>
       </c>
       <c r="B21">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C21" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D21">
         <v>4</v>
       </c>
       <c r="E21" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F21" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G21" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="H21" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
     </row>
     <row r="22" customFormat="1" spans="1:8">
       <c r="A22">
-        <v>10008</v>
+        <v>10006</v>
       </c>
       <c r="B22">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C22" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D22">
         <v>4</v>
       </c>
       <c r="E22" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F22" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G22" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="H22" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
     </row>
     <row r="23" customFormat="1" spans="1:8">
       <c r="A23">
-        <v>10009</v>
+        <v>10007</v>
       </c>
       <c r="B23">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C23" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D23">
         <v>4</v>
       </c>
       <c r="E23" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="F23" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G23" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="H23" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
     </row>
     <row r="24" customFormat="1" spans="1:8">
       <c r="A24">
-        <v>10010</v>
+        <v>10008</v>
       </c>
       <c r="B24">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C24" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D24">
         <v>4</v>
       </c>
       <c r="E24" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F24" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G24" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="H24" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
     </row>
     <row r="25" customFormat="1" spans="1:8">
       <c r="A25">
-        <v>10011</v>
+        <v>10009</v>
       </c>
       <c r="B25">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C25" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D25">
         <v>4</v>
       </c>
       <c r="E25" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F25" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G25" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="H25" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
     </row>
     <row r="26" customFormat="1" spans="1:8">
       <c r="A26">
-        <v>10012</v>
+        <v>10010</v>
       </c>
       <c r="B26">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C26" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D26">
         <v>4</v>
       </c>
       <c r="E26" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F26" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G26" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="H26" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
     </row>
     <row r="27" customFormat="1" spans="1:8">
       <c r="A27">
-        <v>10013</v>
-      </c>
-      <c r="B27" t="s">
-        <v>88</v>
+        <v>10011</v>
+      </c>
+      <c r="B27">
+        <v>11</v>
       </c>
       <c r="C27" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="D27">
         <v>4</v>
       </c>
       <c r="E27" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="F27" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G27" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="H27" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="28" customFormat="1" spans="1:8">
       <c r="A28">
-        <v>20001</v>
-      </c>
-      <c r="B28" t="s">
-        <v>91</v>
+        <v>10012</v>
+      </c>
+      <c r="B28">
+        <v>12</v>
       </c>
       <c r="C28" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D28">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E28" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F28" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G28" t="s">
-        <v>95</v>
+        <v>61</v>
       </c>
       <c r="H28" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="29" customFormat="1" spans="1:8">
       <c r="A29">
-        <v>30001</v>
+        <v>10013</v>
       </c>
       <c r="B29" t="s">
         <v>96</v>
       </c>
       <c r="C29" t="s">
+        <v>93</v>
+      </c>
+      <c r="D29">
+        <v>4</v>
+      </c>
+      <c r="E29" t="s">
         <v>97</v>
       </c>
-      <c r="D29">
+      <c r="F29" t="s">
+        <v>98</v>
+      </c>
+      <c r="G29" t="s">
+        <v>61</v>
+      </c>
+      <c r="H29" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8">
+      <c r="A30">
+        <v>20001</v>
+      </c>
+      <c r="B30" t="s">
+        <v>99</v>
+      </c>
+      <c r="C30" t="s">
+        <v>100</v>
+      </c>
+      <c r="D30">
+        <v>0</v>
+      </c>
+      <c r="E30" t="s">
+        <v>101</v>
+      </c>
+      <c r="F30" t="s">
+        <v>102</v>
+      </c>
+      <c r="G30" t="s">
+        <v>103</v>
+      </c>
+      <c r="H30" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8">
+      <c r="A31">
+        <v>30001</v>
+      </c>
+      <c r="B31" t="s">
+        <v>104</v>
+      </c>
+      <c r="C31" t="s">
+        <v>105</v>
+      </c>
+      <c r="D31">
         <v>10</v>
       </c>
-      <c r="E29" t="s">
-        <v>98</v>
-      </c>
-      <c r="F29" t="s">
-        <v>99</v>
-      </c>
-      <c r="G29" t="s">
-        <v>100</v>
-      </c>
-      <c r="H29" t="s">
+      <c r="E31" t="s">
+        <v>106</v>
+      </c>
+      <c r="F31" t="s">
+        <v>107</v>
+      </c>
+      <c r="G31" t="s">
+        <v>108</v>
+      </c>
+      <c r="H31" t="s">
         <v>45</v>
       </c>
     </row>

--- a/Excel/ResData.xlsx
+++ b/Excel/ResData.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22091" windowHeight="9527"/>
+    <workbookView windowWidth="29868" windowHeight="13380"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="115">
   <si>
     <t>int</t>
   </si>
@@ -354,6 +354,24 @@
   </si>
   <si>
     <t>vfx</t>
+  </si>
+  <si>
+    <t>BGM</t>
+  </si>
+  <si>
+    <t>背景音乐</t>
+  </si>
+  <si>
+    <t>Music/BGM</t>
+  </si>
+  <si>
+    <t>ArtRes/Music/BGM</t>
+  </si>
+  <si>
+    <t>music</t>
+  </si>
+  <si>
+    <t>wav</t>
   </si>
 </sst>
 </file>
@@ -1501,7 +1519,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K31"/>
+  <dimension ref="A1:K32"/>
   <sheetFormatPr defaultColWidth="9.23148148148148" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="12.1759259259259" customWidth="1"/>
@@ -2192,6 +2210,32 @@
         <v>45</v>
       </c>
     </row>
+    <row r="32" spans="1:8">
+      <c r="A32">
+        <v>40001</v>
+      </c>
+      <c r="B32" t="s">
+        <v>109</v>
+      </c>
+      <c r="C32" t="s">
+        <v>110</v>
+      </c>
+      <c r="D32">
+        <v>1</v>
+      </c>
+      <c r="E32" t="s">
+        <v>111</v>
+      </c>
+      <c r="F32" t="s">
+        <v>112</v>
+      </c>
+      <c r="G32" t="s">
+        <v>113</v>
+      </c>
+      <c r="H32" t="s">
+        <v>114</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
